--- a/education_forms/028_child_orientation_registration--education_forms.xlsx
+++ b/education_forms/028_child_orientation_registration--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -862,8 +862,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -891,12 +891,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'morning_-_9am',_'value':_'morning'}</t>
+          <t>morning_-_9am</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Morning - 9AM', 'value': 'morning'}</t>
+          <t>Morning - 9AM</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon_-_2pm',_'value':_'afternoon'}</t>
+          <t>afternoon_-_2pm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon - 2PM', 'value': 'afternoon'}</t>
+          <t>Afternoon - 2PM</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'evening_-_6pm',_'value':_'evening'}</t>
+          <t>evening_-_6pm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Evening - 6PM', 'value': 'evening'}</t>
+          <t>Evening - 6PM</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'visual_arts_and_crafts',_'value':_'art'}</t>
+          <t>visual_arts_and_crafts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Visual Arts and Crafts', 'value': 'art'}</t>
+          <t>Visual Arts and Crafts</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'music_and_rhythm',_'value':_'music'}</t>
+          <t>music_and_rhythm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Music and Rhythm', 'value': 'music'}</t>
+          <t>Music and Rhythm</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'sports_and_outdoor_play',_'value':_'sports'}</t>
+          <t>sports_and_outdoor_play</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Sports and Outdoor Play', 'value': 'sports'}</t>
+          <t>Sports and Outdoor Play</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'science_and_discovery',_'value':_'science'}</t>
+          <t>science_and_discovery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Science and Discovery', 'value': 'science'}</t>
+          <t>Science and Discovery</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_need_childcare',_'value':_true}</t>
+          <t>yes_-_need_childcare</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Need Childcare', 'value': True}</t>
+          <t>Yes - Need Childcare</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_needed',_'value':_false}</t>
+          <t>no_-_not_needed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not Needed', 'value': False}</t>
+          <t>No - Not Needed</t>
         </is>
       </c>
     </row>
